--- a/evals/1_inputs/excel/test_dataset.xlsx
+++ b/evals/1_inputs/excel/test_dataset.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Samuel\Projects\Skripsi\TravelPlanner\TravelPlannerLLMRAGMCP\evals\1_inputs\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7159730D-2362-49C1-8EDC-80ADE9C8866D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22D57998-C564-4002-86DC-9BAAB6D4DC01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{303DDD28-EEF9-48CD-845F-90282090C77A}"/>
   </bookViews>
@@ -53,21 +53,63 @@
     <t>q1</t>
   </si>
   <si>
+    <t>LLM</t>
+  </si>
+  <si>
+    <t>RAG</t>
+  </si>
+  <si>
+    <t>Lokasi apa yang anda sarankan untuk liburan di Indonesia?</t>
+  </si>
+  <si>
+    <t>Hal apa yang membuat Danau Toba menarik?</t>
+  </si>
+  <si>
+    <t>WEATHER</t>
+  </si>
+  <si>
+    <t>FLIGHT</t>
+  </si>
+  <si>
+    <t>HOTEL</t>
+  </si>
+  <si>
+    <t>Apakah hari ini hujan di Bandung?</t>
+  </si>
+  <si>
+    <t>Cari tiket ke Bali</t>
+  </si>
+  <si>
+    <t>Cari hotel di Bali</t>
+  </si>
+  <si>
+    <t>Bali</t>
+  </si>
+  <si>
+    <t>CGK</t>
+  </si>
+  <si>
+    <t>DPS</t>
+  </si>
+  <si>
+    <t>param_departure_id</t>
+  </si>
+  <si>
+    <t>param_arrival_id</t>
+  </si>
+  <si>
+    <t>param_location</t>
+  </si>
+  <si>
+    <t>param_start_date</t>
+  </si>
+  <si>
+    <t>param_end_date</t>
+  </si>
+  <si>
     <t>q2</t>
   </si>
   <si>
-    <t>LLM</t>
-  </si>
-  <si>
-    <t>RAG</t>
-  </si>
-  <si>
-    <t>Lokasi apa yang anda sarankan untuk liburan di Indonesia?</t>
-  </si>
-  <si>
-    <t>Hal apa yang membuat Danau Toba menarik?</t>
-  </si>
-  <si>
     <t>q3</t>
   </si>
   <si>
@@ -75,48 +117,6 @@
   </si>
   <si>
     <t>q5</t>
-  </si>
-  <si>
-    <t>WEATHER</t>
-  </si>
-  <si>
-    <t>FLIGHT</t>
-  </si>
-  <si>
-    <t>HOTEL</t>
-  </si>
-  <si>
-    <t>Apakah hari ini hujan di Bandung?</t>
-  </si>
-  <si>
-    <t>Cari tiket ke Bali</t>
-  </si>
-  <si>
-    <t>Cari hotel di Bali</t>
-  </si>
-  <si>
-    <t>Bali</t>
-  </si>
-  <si>
-    <t>CGK</t>
-  </si>
-  <si>
-    <t>DPS</t>
-  </si>
-  <si>
-    <t>param_departure_id</t>
-  </si>
-  <si>
-    <t>param_arrival_id</t>
-  </si>
-  <si>
-    <t>param_location</t>
-  </si>
-  <si>
-    <t>param_start_date</t>
-  </si>
-  <si>
-    <t>param_end_date</t>
   </si>
 </sst>
 </file>
@@ -487,19 +487,19 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" t="s">
         <v>21</v>
-      </c>
-      <c r="E1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -507,49 +507,49 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" t="s">
         <v>16</v>
-      </c>
-      <c r="D5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" t="s">
-        <v>20</v>
       </c>
       <c r="G5" s="1">
         <v>46275</v>
@@ -560,16 +560,16 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" t="s">
         <v>14</v>
-      </c>
-      <c r="C6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6" t="s">
-        <v>18</v>
       </c>
       <c r="G6" s="1">
         <v>46275</v>
